--- a/ResourcesTH/configTH.xlsx
+++ b/ResourcesTH/configTH.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Params" sheetId="2" r:id="rId2"/>
     <sheet name="Rules" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentManualCount="8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="128">
   <si>
     <t>screenName</t>
   </si>
@@ -64,9 +64,6 @@
     <t>category</t>
   </si>
   <si>
-    <t>DEODORANTS &amp; FRAGRANCES</t>
-  </si>
-  <si>
     <t>brand</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>UUID</t>
   </si>
   <si>
-    <t>AUTODSR_</t>
-  </si>
-  <si>
     <t>Father/Spouse Name</t>
   </si>
   <si>
@@ -184,27 +178,12 @@
     <t>getGeoHierarchyCode</t>
   </si>
   <si>
-    <t>002001</t>
-  </si>
-  <si>
     <t>distributor</t>
   </si>
   <si>
-    <t>50200411</t>
-  </si>
-  <si>
-    <t>0000000098</t>
-  </si>
-  <si>
-    <t>657281537678</t>
-  </si>
-  <si>
     <t>OutletChannel</t>
   </si>
   <si>
-    <t>C01000C11628</t>
-  </si>
-  <si>
     <t>outlet creation upload</t>
   </si>
   <si>
@@ -298,70 +277,139 @@
     <t>DOWNLOAD_UPLOAD</t>
   </si>
   <si>
+    <t>0000000043</t>
+  </si>
+  <si>
+    <t>AXE DEO BODY SPRAY TOUCH 24X50ML</t>
+  </si>
+  <si>
+    <t>BREEZE</t>
+  </si>
+  <si>
+    <t>BREEZE COLOR LN RGLR 500G</t>
+  </si>
+  <si>
+    <t>บริษัท ศุภaมิตร แอล วี จำกัด</t>
+  </si>
+  <si>
+    <t>shahmeer DM PJP</t>
+  </si>
+  <si>
+    <t>Korangi Section</t>
+  </si>
+  <si>
+    <t>testID</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>50000598</t>
+  </si>
+  <si>
+    <t>50000598-0000000045-Leopard PJP OB</t>
+  </si>
+  <si>
+    <t>587152469812-Korangi Section</t>
+  </si>
+  <si>
+    <t>MPM_Mom &amp; Pop Medium</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Temporary Price Reduction</t>
+  </si>
+  <si>
+    <t>Temporary_price_reduction.xlsx</t>
+  </si>
+  <si>
+    <t>PRICE_DEDUCTION</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>bulk order upload</t>
+  </si>
+  <si>
+    <t>DYL_LMT_ORDER_CREATION</t>
+  </si>
+  <si>
+    <t>LMT</t>
+  </si>
+  <si>
+    <t>LmtOrderCreationExcel.xlsx</t>
+  </si>
+  <si>
+    <t>HAIR CARE</t>
+  </si>
+  <si>
+    <t>CLEAR</t>
+  </si>
+  <si>
+    <t>CLEAR BANDED HC VIOLT 200ML</t>
+  </si>
+  <si>
+    <t>002-TH</t>
+  </si>
+  <si>
+    <t>AUTO_</t>
+  </si>
+  <si>
+    <t>Start Date*</t>
+  </si>
+  <si>
+    <t>End Date*</t>
+  </si>
+  <si>
+    <t>DSR Code</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>0000000043</t>
-  </si>
-  <si>
-    <t>AXE</t>
-  </si>
-  <si>
-    <t>AXE DEO N GRMNG TOUCH 50ML</t>
-  </si>
-  <si>
-    <t>AXE DEO BODY SPRAY TOUCH 24X50ML</t>
-  </si>
-  <si>
-    <t>BREEZE</t>
-  </si>
-  <si>
-    <t>BREEZE COLOR LN RGLR 500G</t>
-  </si>
-  <si>
-    <t>บริษัท ศุภaมิตร แอล วี จำกัด</t>
-  </si>
-  <si>
-    <t>shahmeer DM PJP</t>
-  </si>
-  <si>
-    <t>Korangi Section</t>
-  </si>
-  <si>
-    <t>testID</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>PO_NUMBER</t>
+  </si>
+  <si>
+    <t>Bulk Order Upload</t>
+  </si>
+  <si>
+    <t>5047C</t>
   </si>
 </sst>
 </file>
@@ -385,18 +433,35 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -405,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -423,6 +488,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -704,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="31.54296875" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.08984375" customWidth="1"/>
@@ -716,7 +786,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -731,12 +801,12 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -745,193 +815,251 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -951,7 +1079,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -965,163 +1093,163 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
+      <c r="D2" s="4" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>92</v>
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>93</v>
+        <v>13</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4" t="str">
-        <f ca="1" xml:space="preserve"> TEXT(TODAY() - 6, "yyyy-mm-dd")</f>
-        <v>2025-10-21</v>
+        <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "dd-mm-yyyy")</f>
+        <v>12-12-2025</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="D8" s="5" t="str">
-        <f ca="1">TEXT(TODAY(), "yyyy-mm-dd")</f>
-        <v>2025-10-27</v>
+        <f ca="1">TEXT(TODAY()+2, "dd-mm-yyyy")</f>
+        <v>18-12-2025</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>4</v>
@@ -1130,119 +1258,119 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1252,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24.36328125" customWidth="1"/>
@@ -1264,76 +1392,76 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E2" s="2">
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2">
         <v>11</v>
@@ -1342,53 +1470,56 @@
     </row>
     <row r="5" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2">
         <v>6</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2">
         <v>4</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2">
         <v>4</v>
@@ -1396,16 +1527,16 @@
     </row>
     <row r="8" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="E8" s="2">
         <v>4</v>
@@ -1413,16 +1544,16 @@
     </row>
     <row r="9" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2">
         <v>4</v>
@@ -1430,70 +1561,132 @@
     </row>
     <row r="10" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="2">
-        <v>5</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E12" s="2">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="E13" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/ResourcesTH/configTH.xlsx
+++ b/ResourcesTH/configTH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Screens" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="126">
   <si>
     <t>screenName</t>
   </si>
@@ -397,9 +397,6 @@
     <t>DSR Code</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
@@ -407,9 +404,6 @@
   </si>
   <si>
     <t>Bulk Order Upload</t>
-  </si>
-  <si>
-    <t>5047C</t>
   </si>
 </sst>
 </file>
@@ -881,7 +875,7 @@
         <v>114</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1675,18 +1669,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>127</v>
+        <v>22</v>
+      </c>
+      <c r="E17" s="2">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
